--- a/astro-site/public/dl/kit-tareas-heladeria/02-partidas-produccion.xlsx
+++ b/astro-site/public/dl/kit-tareas-heladeria/02-partidas-produccion.xlsx
@@ -967,7 +967,7 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Pasteurizar a 85 °C durante 15 segundos (alta pasteurización)</t>
+          <t>Añadir grasas y emulsionantes al alcanzar 40-50 °C en ascenso</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Añadir grasas y emulsionantes al alcanzar 40-50 °C en descenso</t>
+          <t>Pasteurizar a 85 °C durante 15 segundos (alta pasteurización)</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Limpiar mantecadora: desmontar cuchillas, junta, cilindro</t>
+          <t>Limpiar mantecadora: desmontar cuchillas, batidor y junta; el cilindro se limpia en su sitio</t>
         </is>
       </c>
       <c r="C24" s="15" t="inlineStr">
